--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tabA3_cord_adequacy.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tabA3_cord_adequacy.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Niacin</t>
   </si>
   <si>
-    <t xml:space="preserve">3679.4% [Exceeds UL (100% of obs)]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3606.1% [Exceeds UL (100% of obs)]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1969.7% [Exceeds UL (51.4% of obs)]</t>
+    <t xml:space="preserve">118% [Always within range]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.5% [Always within range]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.4% [Below min (8.8% of obs)]</t>
   </si>
   <si>
     <t xml:space="preserve">Phosphorus</t>
